--- a/data/UV-Vis/Sb2Se3_JOliveira_7abr26.xlsx
+++ b/data/UV-Vis/Sb2Se3_JOliveira_7abr26.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fbdd27f2520478cf/Ambiente de Trabalho/TESE/Data_Analysis/data/UV-Vis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF5E0754-578D-4348-8A24-C9D385C11D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{DF5E0754-578D-4348-8A24-C9D385C11D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11AB2018-6495-4A71-835B-9A2F828A5C22}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{59E5274C-A030-4F5B-AE5A-72D58531B503}"/>
+    <workbookView xWindow="3036" yWindow="3036" windowWidth="17280" windowHeight="8880" xr2:uid="{59E5274C-A030-4F5B-AE5A-72D58531B503}"/>
   </bookViews>
   <sheets>
     <sheet name="Sb2Se3" sheetId="3" r:id="rId1"/>

--- a/data/UV-Vis/Sb2Se3_JOliveira_7abr26.xlsx
+++ b/data/UV-Vis/Sb2Se3_JOliveira_7abr26.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="4" documentId="8_{DF5E0754-578D-4348-8A24-C9D385C11D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11AB2018-6495-4A71-835B-9A2F828A5C22}"/>
   <bookViews>
-    <workbookView xWindow="3036" yWindow="3036" windowWidth="17280" windowHeight="8880" xr2:uid="{59E5274C-A030-4F5B-AE5A-72D58531B503}"/>
+    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="8880" xr2:uid="{59E5274C-A030-4F5B-AE5A-72D58531B503}"/>
   </bookViews>
   <sheets>
     <sheet name="Sb2Se3" sheetId="3" r:id="rId1"/>
@@ -16701,6 +16701,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
